--- a/data_cuti_smkn1koba.xlsx
+++ b/data_cuti_smkn1koba.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,20 +434,25 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Keterangan</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Tgl_mulai_cuti</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Tgl_selesai_cuti</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Tahun_cuti</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Jumlah_hari_cuti</t>
         </is>
@@ -459,20 +464,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FENDI BOY PARNINGOTAN SITOMPUL</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>46266</v>
+          <t>LISMASARI</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ada acara keluarga.</t>
+        </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2026</v>
+        <v>46311</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>46311</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2026</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +491,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FENDI BOY PARNINGOTAN SITOMPUL</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>46260</v>
+          <t>LISMASARI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ada urusan/acara keluarga.</t>
+        </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2026</v>
+        <v>46287</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46289</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>2026</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -503,20 +518,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FENDI BOY PARNINGOTAN SITOMPUL</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>46230</v>
+          <t>LISMASARI</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ada urusan keluarga dan jemput anak di pondok.</t>
+        </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46230</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2026</v>
+        <v>46191</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46192</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2026</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -525,19 +545,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FENDI BOY PARNINGOTAN SITOMPUL</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>46227</v>
+          <t>LISMASARI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ada urusan keluarga.</t>
+        </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46227</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2026</v>
+        <v>46176</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46176</v>
       </c>
       <c r="F5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -547,20 +572,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FENDI BOY PARNINGOTAN SITOMPUL</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>46217</v>
+          <t>LISMASARI</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ada urusan keluarga.</t>
+        </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46219</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2026</v>
+        <v>46168</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46168</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2026</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -569,20 +599,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FENDI BOY PARNINGOTAN SITOMPUL</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>46190</v>
+          <t>LISMASARI</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ada acara keluarga.</t>
+        </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46192</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2026</v>
+        <v>46164</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46164</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2026</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -591,19 +626,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FENDI BOY PARNINGOTAN SITOMPUL</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>46175</v>
+          <t>LISMASARI</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Menjemput anak di pondok.</t>
+        </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46175</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2026</v>
+        <v>46094</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46094</v>
       </c>
       <c r="F8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -613,19 +653,105 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FENDI BOY PARNINGOTAN SITOMPUL</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>46154</v>
+          <t>LISMASARI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ada acara urusan keluarga.</t>
+        </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46155</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2026</v>
+        <v>46085</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46087</v>
       </c>
       <c r="F9" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LISMASARI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ada acara keluarga.</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LISMASARI</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ada acara keluarga.</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LISMASARI</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Menghadiri acara keluarga.</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45933</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>45936</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G12" t="n">
         <v>2</v>
       </c>
     </row>
